--- a/www/download/COUNTRY.JPN.EXI382.xlsx
+++ b/www/download/COUNTRY.JPN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Japão</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3891527607362</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.38955950920245</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>48.803</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>66.915</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>67.155</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>67.829</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>67.333</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>66.79</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>66.646</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>66.219</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>65.268</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>65.019</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>65.021</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>65.235</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>65.604</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>65.825</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>65.522</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>63.02</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>62.76</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>62.505</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>62.04</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>48.161</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>48.057</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>49.902</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>53.002</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>49.53</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>48.857</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>51.94</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>51.548</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>42.509</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>55.014</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>55.576</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>56.214</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>55.968</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>55.6</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>55.836</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>55.913</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>55.379</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>55.368</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>55.511</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>56.733</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>57.145</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>57.137</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>54.88</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>54.93</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>54.89</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>54.62</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>42.477</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>42.542</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>43.861</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>46.66</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>43.486</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>42.956</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>45.652</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>45.244</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>101440.282</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>140587.261</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>141113.841</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>142519.138</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>141360.688</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>140220.689</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>139912.613</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>138925.01</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>136864.824</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>136296.395</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>136155.834</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>136440.812</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>137208.122</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>137628.494</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>136904.573</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>131598.74</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>130974.376</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>130488.098</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>129563.512</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>100569.273</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>100026.584</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>104167.667</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>110588.624</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>103124.536</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>101881.747</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>108273.336</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>107412.313</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>88458.448</t>
+          <t>486480779362.013</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>91504.531</t>
+          <t>207499925761.946</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>93346.987</t>
+          <t>208449872953.665</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94590.89</t>
+          <t>187484627058.431</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>94538.248</t>
+          <t>192320826438.498</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>94104.871</t>
+          <t>197199182420.469</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>95336.201</t>
+          <t>204180322400.862</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96427.936</t>
+          <t>198157713658.555</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>96057.136</t>
+          <t>182539612517.585</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>96469.953</t>
+          <t>196445010654.637</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>96930.934</t>
+          <t>208982777364.177</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>97508.772</t>
+          <t>194190944814.576</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>100568.604</t>
+          <t>176916381125.415</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>101784.846</t>
+          <t>196703184183.443</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>102284.141</t>
+          <t>172266687845.611</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>98067.684</t>
+          <t>181148247828.662</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>98722.52</t>
+          <t>189353226514.288</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>99097.518</t>
+          <t>184172553263.607</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>98941.44</t>
+          <t>181543592248.129</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>88838.03</t>
+          <t>150321314186.451</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>88650.991</t>
+          <t>150002121583.34</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>91689.867</t>
+          <t>172031570299.638</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>97495.336</t>
+          <t>165091893532.556</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>90666.051</t>
+          <t>174383125693.791</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>89691.192</t>
+          <t>169875228524.936</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>95280.071</t>
+          <t>180363948180.092</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>94388.316</t>
+          <t>170099129587.366</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>147702787366.353</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>98525701800.3275</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>85675997860.2349</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>86272806384.8296</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>91959468000.2643</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>109813709965.54</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>106738675670.212</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>90629298509.4434</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>82382727904.3439</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>87139822028.9441</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>84862210515.1992</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>80197338004.9139</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>62477873822.2675</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>68442174205.2681</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>60818084026.1971</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>67467828822.6489</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>64784812626.7189</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>70478639138.6506</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>63064885042.141</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>62137684954.4453</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>56131113172.2563</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>53476323925.4137</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>50240204981.6393</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>57174824248.6467</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>55339691820.7626</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>58810105567.3047</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>70549041813.3058</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>135582176.006572</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6189700.69261733</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5305290.94334534</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4989795.49077051</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4192752.63695643</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3518712.27637103</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3884005.85711672</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4145847.21116145</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4037555.81185885</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4651752.33741325</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5243997.92547924</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5408508.22176915</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4417923.37330835</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4933447.99168257</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4355247.18308277</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4032829.66929527</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4094109.86744255</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3502670.53687112</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4147521.76226445</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>86315529.1375262</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>71118227.5031188</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>76994632.3202001</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>87256250.9049141</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>86869424.1139402</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>79081404.7354449</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>83919386.0280922</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>83916961.3910207</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>202878.638706861</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>663590.337019303</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>722553.638404592</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>748932.414487031</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>775338.418927447</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>914923.14041521</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>913598.775546179</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>872930.452102856</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>787829.403722177</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>720406.932357746</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>765329.597534409</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>818071.234318035</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>850676.26025606</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>857459.635373884</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>790727.31205098</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>937398.770891669</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>967591.941376177</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1073633.03197186</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1050795.08866609</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>836101.641751135</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>977637.888113015</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>900437.035006606</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>997604.42626385</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>930728.780500083</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>947644.407013506</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>949933.188695393</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>919251.310214494</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1813407.03820657</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1576806.96500735</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1725261.2252146</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1595295.63396204</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1726136.12240754</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2115713.24452754</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2199583.87074838</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2069289.01495371</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1751062.62733231</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1841558.38811987</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2100229.21774878</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2087612.83680221</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1970479.11074837</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2201405.56010992</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1931996.58952167</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2342855.45470953</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2549510.68695198</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2737052.61156957</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2635464.5614244</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2258763.96940193</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2546158.08290328</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2661575.73444064</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2700423.06791629</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2774166.05486417</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2879363.16480796</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2908270.73025955</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2692781.51420951</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.401105083594002</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.071262327209996</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.0895348677736836</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.0964160546494801</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.0280425719701614</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.143049888492703</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.106826083410186</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0639819306334899</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.165986347423819</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.107070805904968</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.142215521037615</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.215860456540095</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.60966751663272</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.487165584406286</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.681804723672926</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.453547353032384</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.523852829039483</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.406064578020567</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.56888322136635</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.429696481810532</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.579355646597483</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.714588068564982</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.9405839599814</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.585768774767929</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.620738908882011</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.620130927151476</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.337910675548578</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3474.64261011679</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1790.91075957192</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1541.61174796541</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1534.72919208023</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1643.05757703476</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1975.0631737266</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1911.63247756333</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1620.90141111362</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1487.62749337005</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1573.8215193343</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1528.73207380841</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1437.2411581626</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1101.26741407134</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1197.68684747945</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1064.42184822137</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1229.37005872167</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1179.40674725477</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1283.997798117</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1154.61158993292</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1462.86050677641</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1319.41332181493</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1219.23200937788</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1076.72420719052</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1314.78460688962</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1288.28792946592</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1288.22488403361</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1559.31802937874</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.532</t>
+          <t>262658033221.829</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>88897121784.2558</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>85700203073.5934</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>81313004064.5962</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.516</t>
+          <t>91453904617.7206</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>95791679528.4485</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.938</t>
+          <t>100003849706.896</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>97164378082.8789</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>88093913742.326</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.159</t>
+          <t>107201782129.369</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>100924578148.857</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>91173266855.1364</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>66199552221.0888</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>76121672866.623</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.206</t>
+          <t>62778733602.3234</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2.462</t>
+          <t>75862826784.9339</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2.566</t>
+          <t>68338982056.9783</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>66097990033.1625</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>57528316471.1736</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>53765990041.9075</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>60733891098.1798</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2.343</t>
+          <t>73073941273.1988</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2.188</t>
+          <t>73915866849.1682</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>75250977627.575</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.397</t>
+          <t>74280449600.1105</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>78674103332.5437</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2.559</t>
+          <t>84115869178.2769</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>330415820571.616</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>108577404439.434</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>105985026465.904</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>100186467130.108</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>112127405797.948</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>117321898787.117</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>119850042706.785</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>117062354765.274</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>104979621553.173</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>127249929813.657</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>119241087563.109</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>108255008814.55</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>79922861061.5773</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>92183089543.9559</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>76860768161.6494</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>90328912682.5431</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>83256198812.0281</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>82369322475.467</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>73651311755.1658</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>69428014271.6401</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>76063534807.8368</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>88447762791.5905</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>83094084711.7847</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>85735488198.8591</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>83731591619.2492</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>88959262259.4064</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>94499972075.9145</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-67757787349.7868</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-19680282655.1784</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-20284823392.3103</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-18873463065.5123</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-20673501180.2276</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-21530219258.6681</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-19846192999.8896</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-19897976682.3947</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-16885707810.8473</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-20048147684.2872</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-18316509414.2519</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-17081741959.4136</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-13723308840.4886</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-16061416677.3329</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-14082034559.326</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-14466085897.6092</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-14917216755.0498</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-16271332442.3046</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-16122995283.9922</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-15662024229.7326</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-15329643709.657</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-15373821518.3918</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-9178217862.61657</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-10484510571.284</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-9451142019.13871</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-10285158926.8627</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-10384102897.6376</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7.638</t>
+          <t>2080.94579552662</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.052</t>
+          <t>1663.2862910194</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.358</t>
+          <t>1679.63975197785</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6.674</t>
+          <t>1682.70172573599</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7.967</t>
+          <t>1689.13313738988</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9.985</t>
+          <t>1692.53060695896</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8.966</t>
+          <t>1707.42026706553</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>1724.60981276322</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.312</t>
+          <t>1734.5533473218</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7.257</t>
+          <t>1742.33185776</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>1746.14150221198</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>6.935</t>
+          <t>1747.48469072179</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>6.511</t>
+          <t>1772.67438355675</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>6.951</t>
+          <t>1781.1586604675</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>7.221</t>
+          <t>1790.14969231936</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>8.171</t>
+          <t>1786.94759475215</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>8.727</t>
+          <t>1797.24230839244</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>9.207</t>
+          <t>1805.38382218872</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>7.432</t>
+          <t>1811.45075064089</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>7.174</t>
+          <t>2091.44651991781</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>7.719</t>
+          <t>2083.82288000434</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>8.673</t>
+          <t>2090.48065609183</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>8.305</t>
+          <t>2089.47372579761</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>8.267</t>
+          <t>2084.94437515108</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>8.896</t>
+          <t>2087.97837312846</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>8.953</t>
+          <t>2087.09297574898</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>9.023</t>
+          <t>2086.22823808119</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.532</t>
+          <t>2078.58566417973</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>2100.97961446698</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2101.32173723997</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>2101.16585039361</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.516</t>
+          <t>2099.42655161671</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>2099.42639616678</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.938</t>
+          <t>2099.33999039696</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>2097.96297135329</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>2096.98278622569</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.159</t>
+          <t>2096.26776030263</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2094.02216507913</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2091.53415048331</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>2091.44694563185</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>2090.82406380587</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.206</t>
+          <t>2089.45073242796</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.462</t>
+          <t>2088.20596635979</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.566</t>
+          <t>2086.90847673642</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2087.64255659449</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>2088.3867182465</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>2088.20913869235</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>2081.41656804973</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2.343</t>
+          <t>2087.43631680987</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2.188</t>
+          <t>2086.50423244269</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>2082.05893144268</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2.397</t>
+          <t>2085.28689034791</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>2084.56884717042</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2.559</t>
+          <t>2083.73887661681</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>448325.123436488</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>424523.279118692</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>487331.296428256</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>447346.353872308</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>506115.082542986</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>675197.315671336</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>585700.013864644</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>570740.0150256</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>539455.701041039</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>586643.72119496</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>624632.343315531</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>666006.114959629</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>663665.20462686</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>681793.953809883</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>531828.198717662</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>750867.89513509</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>758792.551969344</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>812167.629643616</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>702424.418226424</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>731235.004026042</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>806528.663600976</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>841706.550553631</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>909600.351992904</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>922101.487392171</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>943148.454212814</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>945799.291082166</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>967969.22555162</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>46778303673.3997</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>12291858917.2335</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>13582181903.502</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>12164856806.0415</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>12369457886.7977</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>15334849292.7012</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15119102888.7106</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>15885820331.7369</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>15170149712.6724</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>18027917717.3908</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20488323129.844</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>21839387191.5148</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>17803274610.8137</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>22587448062.4841</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>16079251227.4066</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>20242988463.818</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>21412862447.6762</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>19794786914.2809</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>19833791488.4803</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>21547815233.7461</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>20450993959.62</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>21226888210.8395</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>22587036520.5383</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>23133345552.9586</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>21864060201.1879</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>23032441732.5377</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>22916507875.9519</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>379442.200255465</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>402930.166992893</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>433509.285999712</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>361863.465335507</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>419078.398302268</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>576264.357166345</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>544213.212242237</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>493847.65978923</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>452300.872185387</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>484278.557078104</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>549168.073251655</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>599272.10457231</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>582100.223339276</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>661675.065640087</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>504800.597182945</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>668729.132994589</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>790210.538331018</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>909840.112377441</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>820060.54513549</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>848960.69388846</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>828214.65470982</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>784062.289848869</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>857179.848239591</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>909298.290663062</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>927905.772028794</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>940430.755886827</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>970447.065264423</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>101440.282</t>
+          <t>270412353446.05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>140587.261</t>
+          <t>96802598036.3699</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>141113.841</t>
+          <t>89207565710.5813</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>142519.138</t>
+          <t>77373028236.5499</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>141360.688</t>
+          <t>87857014326.0989</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>140220.689</t>
+          <t>95778012417.7443</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>139912.613</t>
+          <t>108432003191.432</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>138925.01</t>
+          <t>100183527587.533</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>136864.824</t>
+          <t>88458405324.6154</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>136296.395</t>
+          <t>106456968608.926</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>136155.834</t>
+          <t>108791458015.483</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>136440.812</t>
+          <t>103083187220.392</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>137208.122</t>
+          <t>73873891371.9229</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>137628.494</t>
+          <t>95952041582.7181</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>136904.573</t>
+          <t>74879754051.3398</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>131598.74</t>
+          <t>85977940253.4807</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>130974.376</t>
+          <t>93374833332.1753</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>130488.098</t>
+          <t>96542128027.9654</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>129563.512</t>
+          <t>90837744706.213</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>100569.273</t>
+          <t>87828763356.6864</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>100026.584</t>
+          <t>83281158859.7977</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>104167.667</t>
+          <t>88187279118.9163</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>110588.624</t>
+          <t>91453615923.6496</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>103124.536</t>
+          <t>97111817219.7841</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>101881.747</t>
+          <t>94753349736.3932</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>108273.336</t>
+          <t>101185575288.755</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>107412.313</t>
+          <t>107273805549.971</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>88458.448</t>
+          <t>68882.9231810236</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>91504.531</t>
+          <t>21593.1121257989</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>93346.987</t>
+          <t>53822.0104285443</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>94590.89</t>
+          <t>85482.888536801</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>94538.248</t>
+          <t>87036.6842407176</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>94104.871</t>
+          <t>98932.9585049916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>95336.201</t>
+          <t>41486.8016224065</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96427.936</t>
+          <t>76892.3552363707</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>96057.136</t>
+          <t>87154.8288556523</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>96469.953</t>
+          <t>102365.164116857</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>96930.934</t>
+          <t>75464.2700638756</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>97508.772</t>
+          <t>66734.0103873193</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>100568.604</t>
+          <t>81564.9812875842</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>101784.846</t>
+          <t>20118.888169796</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>102284.141</t>
+          <t>27027.6015347163</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>98067.684</t>
+          <t>82138.7621405012</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>98722.52</t>
+          <t>-31417.986361674</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>99097.518</t>
+          <t>-97672.4827338257</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>98941.44</t>
+          <t>-117636.126909067</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>88838.03</t>
+          <t>-117725.689862419</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>88650.991</t>
+          <t>-21685.991108844</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>91689.867</t>
+          <t>57644.2607047621</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>97495.336</t>
+          <t>52420.5037533127</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>90666.051</t>
+          <t>12803.1967291095</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>89691.192</t>
+          <t>15242.6821840205</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>95280.071</t>
+          <t>5368.53519533951</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>94388.316</t>
+          <t>-2477.83971280199</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>469931.351</t>
+          <t>-223634049772.651</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>215049.25</t>
+          <t>-84510739119.1364</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>217652.102</t>
+          <t>-75625383807.0794</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>196294.649</t>
+          <t>-65208171430.5084</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>199707.194</t>
+          <t>-75487556439.3012</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>204193.465</t>
+          <t>-80443163125.043</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>210279.885</t>
+          <t>-93312900302.7216</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>203744.64</t>
+          <t>-84297707255.796</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>190026.565</t>
+          <t>-73288255611.943</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>201900.432</t>
+          <t>-88429050891.5355</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>214529.185</t>
+          <t>-88303134885.6392</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>199638.379</t>
+          <t>-81243800028.8769</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>186184.631</t>
+          <t>-56070616761.1092</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>202514.532</t>
+          <t>-73364593520.2341</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>178370.143</t>
+          <t>-58800502823.9332</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>186593.415</t>
+          <t>-65734951789.6627</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>193952.764</t>
+          <t>-71961970884.4991</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>188225.343</t>
+          <t>-76747341113.6846</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>185777.16</t>
+          <t>-71003953217.7327</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>151743.019</t>
+          <t>-66280948122.9403</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>151521.897</t>
+          <t>-62830164900.1777</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>173757.19</t>
+          <t>-66960390908.0768</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>167391.922</t>
+          <t>-68866579403.1113</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>175413.42</t>
+          <t>-73978471666.8255</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>171666.925</t>
+          <t>-72889289535.2053</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>181465.689</t>
+          <t>-78153133556.217</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>170038.513</t>
+          <t>-84357297674.019</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>2408629.41442437</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>2242805.06475139</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>2266791.25452512</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>2022920.4860985</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>2412925.16859755</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.901</t>
+          <t>3316387.42511162</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>2925137.61343293</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>2534586.45731431</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2120732.89443655</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>2041231.75285666</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>2237500.55637091</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1934916.84571021</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1699083.86795552</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.992</t>
+          <t>1803064.25556108</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>2125856.53036571</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2320175.93833741</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2.279</t>
+          <t>2467186.56873073</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2496063.84182638</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2.341</t>
+          <t>1950294.59378733</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.965</t>
+          <t>2017112.82335783</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2170238.23724788</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2257821.90941757</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2.304</t>
+          <t>2241491.53175762</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2.347</t>
+          <t>2141058.83286348</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2.429</t>
+          <t>2308184.16332419</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2.446</t>
+          <t>2317463.17675382</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2.249</t>
+          <t>2415033.93706496</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>54426.037</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>87325.176</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>87300.527</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>88017.112</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>86385.844</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>85277.197</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>84806.447</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>83592.916</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>82127.316</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>76848.146</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>76153.928</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>76097.456</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>76376.636</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>76616.978</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>70505.288</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>72479.138</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>71863.459</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>72243.309</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>72383.867</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>55642.776</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>57595.7</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>58199.958</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>60989.112</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>58505.292</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>55908.651</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>58912.569</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>58067.781</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>3523720.68318381</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>3118644.02174256</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>3173563.45940162</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>2953041.39262112</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>3502634.12933994</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>4634459.05994517</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>4089911.79990845</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>3504823.46149419</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>3106099.1122097</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>3004763.76507818</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>3131770.2136553</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>2926998.17073158</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>2502813.24650446</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>2744133.51547049</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>3070384.62397411</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>3427392.75132963</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>3571465.85778109</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>3804567.49510953</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>2953492.03452023</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>2925109.44412302</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>3140143.54285605</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>3261770.59038817</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>3045441.90602695</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>3082581.39166052</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>3336905.12422255</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>3353034.89964347</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>3562388.82133835</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>128925.79</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>89474.902</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>79508.888</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>79841.785</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>83922.642</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>100369.164</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>96256.855</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>82436.79</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>76977.033</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>79819.335</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>78173.773</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>73967.196</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>60134.445</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>62931.712</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>55587.168</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>61445.076</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>58702.035</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>63071.358</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>57108.182</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>55847.248</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>50012.506</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>48448.786</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>45280.996</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>51460.943</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>49978.809</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>52777.098</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>61949.078</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-31.39</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>18.47</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-6.24</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>24.79</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>20.86</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>23.99</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>67.24</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>84.01</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>68.18</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>57.12</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>73.25</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>59.07</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>77.26</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>89.25</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>115.31</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>76.18</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>79.46</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>80.53</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>52.36</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>185.097</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>8.206</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>7.099</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6.685</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>5.579</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>4.597</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5.094</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>5.443</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>5.391</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6.083</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>6.871</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>7.012</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>5.955</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6.471</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>5.665</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>5.218</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>5.275</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>4.539</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>5.419</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>119.671</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>98.528</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>106.717</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>120.976</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>120.499</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>109.647</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>116.366</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>116.302</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1677380.89304176</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1691570.17785686</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1726005.6753359</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1558312.15630101</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1875759.97554916</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1999878.15806016</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1899108.88773251</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1977533.1506944</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1856556.99987139</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1875657.0941298</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1619747.41150479</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1511459.58292344</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1650898.94517079</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1430803.07629884</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1633877.95785592</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1941442.86783176</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1968595.21216255</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2258911.630644</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1987697.41140427</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1674176.44097038</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>1802300.44920263</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2329264.35860792</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2325873.96904494</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>2190470.37728013</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2370591.19024783</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>2381105.70139495</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2158343.87985841</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>88458448492.7047</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>91504531000.0381</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>93346987000.0294</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>94590889999.9933</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>94538247999.9995</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>94104870999.9994</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>95336200999.9727</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>96427936000.0365</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>96057135999.9963</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>96469952999.9986</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>96930934000.022</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>97508771999.9549</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>100568603999.982</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>101784846000.014</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>102284140999.995</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>98067684000.0033</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>98722520000.0185</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>99097517999.9505</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>98941440000.0128</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>88838029567.2216</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>88650990538.4053</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>91689866953.2304</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>97495335933.547</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>90666050996.3481</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>89691191739.4495</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>95280070858.6335</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>94388316191.7448</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>101440282020.024</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>140587261000.024</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>141113841000.018</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>142519137999.993</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>141360688000.003</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>140220689000.003</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>139912612999.989</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>138925010000.026</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>136864823999.987</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>136296394999.995</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>136155834000.024</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>136440811999.978</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>137208121999.979</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>137628494000.021</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>136904573000.004</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>131598740000</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>130974376000.005</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>130488097999.952</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>129563512000.019</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>100569273282.559</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>100026583826.806</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>104167667406.275</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>110588623819.857</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>103124536423.079</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>101881747338.533</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>108273335859.043</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>107412313431.307</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>54426036843.679</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>87325175955.9603</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>87300526973.1898</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>88017111958.9565</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>86385843828.8558</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>85277197055.945</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>84806446808.7704</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>83592915886.3778</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>82127316202.5599</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>76848145796.3306</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>76153928123.7062</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>76097455963.7168</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>76376635840.9382</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>76616977645.1348</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>70505287522.1743</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>72479138447.2414</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>71863458736.015</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>72243308707.5425</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>72383866550.6584</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>55642775997.8649</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>57595700102.7962</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>58199958424.5124</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>60989111552.5992</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>58505291574.8122</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>55908650971.6234</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>58912569121.4844</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>58067781182.5493</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>48802550.5843445</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>66915100.0000025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>67154800.000007</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>67828599.9999928</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>67332999.9999976</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>66790000.0000114</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>66645999.9999969</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>66218999.9999917</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>65267500.0000009</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>65018599.999992</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>65021199.9999911</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>65234800.0000138</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>65604399.999985</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>65824999.9999996</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>65521800.0000025</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>63020000.0000026</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>62760000.0000127</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>62505000.0000063</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>62040000.0000029</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>48160536.9017475</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>48056974.9286325</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>49902201.3593543</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>53001868.9156407</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>49530075.6696753</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>48857424.7553704</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>51940398.1336536</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>51547876.0974616</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>42508771.0995946</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>55014300.0000055</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>55575600.0000055</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>56213699.9999931</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>55968499.9999965</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>55600100.000012</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>55836399.9999971</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>55912899.999993</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>55378600.0000008</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>55368299.9999916</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>55511499.9999894</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>55799500.0000139</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>56732699.9999841</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>57145300.0000004</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>57137200.0000031</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>54880000.000003</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>54930000.0000122</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>54890000.0000065</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>54620000.0000041</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>42476835.396543</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>42542478.7245932</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>43860662.7074203</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>46660235.4123072</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>43486076.6919876</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>42955996.5245537</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>45652049.0297952</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>45243523.440445</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>101440282020.024</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>140587261000.024</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>141113841000.018</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>142519137999.993</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>141360688000.003</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>140220689000.003</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>139912612999.989</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>138925010000.026</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>136864823999.987</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>136296394999.995</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>136155834000.024</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>136440811999.978</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>137208121999.979</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>137628494000.021</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>136904573000.004</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>131598740000</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>130974376000.005</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>130488097999.952</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>129563512000.019</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>100569273282.559</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>100026583826.806</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>104167667406.275</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>110588623819.857</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>103124536423.079</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>101881747338.533</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>108273335859.043</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>107412313431.307</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>88458448492.7047</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>91504531000.0381</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>93346987000.0294</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>94590889999.9933</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>94538247999.9995</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>94104870999.9994</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>95336200999.9727</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96427936000.0365</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>96057135999.9963</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>96469952999.9986</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>96930934000.022</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>97508771999.9549</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>100568603999.982</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>101784846000.014</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>102284140999.995</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>98067684000.0033</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>98722520000.0185</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>99097517999.9505</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>98941440000.0128</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>88838029567.2216</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>88650990538.4053</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>91689866953.2304</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>97495335933.547</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>90666050996.3481</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>89691191739.4495</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>95280070858.6335</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>94388316191.7448</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10627182.4204631</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>9812102.18058482</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10238281.1927173</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>9286239.61959106</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>11086378.4830545</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>13893825.9682117</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>12476560.984242</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>11340252.2669083</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>10175083.3143556</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10099082.6429564</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10204569.6996867</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>9650004.22497911</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>9060080.29203513</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>9672906.78959293</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>10048940.1343891</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>11371111.3892627</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>12143830.4858726</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>12811809.9570958</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>10342082.7130001</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>9983369.70646028</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>10741728.7629672</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>12069148.8009229</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>11556869.8158417</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11504015.544107</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>12378955.1481231</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12458057.3528912</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>12555468.6038892</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4119198.25299078</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3605575.88811016</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3691101.4897913</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3446671.1141339</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>4080355.08878247</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5363573.23332861</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4787414.66891026</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4078096.72886439</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>3612270.66925794</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>3511159.7056319</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>3699584.39059906</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>3509702.3324658</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2933991.76945508</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>3335816.45500757</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>3585503.73410666</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>4041960.75627114</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>4187075.69679185</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>4459812.67479589</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>3414459.58798674</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>3406577.72777483</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>3703096.36332747</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>3859069.49923248</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>3669015.05812505</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>3647585.51270002</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>3946970.15320514</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>3965892.08112325</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>4217417.17808272</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
